--- a/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam est au bord de la mer avec maman. Des galets sont sur le sable. Maman dit : on compte des objets. Adam touche un galet. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Adam dit : cinq galets. Maman en pose encore. Six. Sept. Huit. Neuf. Dix. Adam répète : dix. Il a compté des objets. Les galets sont lisses. Maman dit : tu as dit le nombre.</t>
+          <t>Adam est au bord de la mer avec maman. Des galets sont sur le sable. On compte des objets. Adam touche un galet. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Maman en pose encore. Six. Sept. Huit. Neuf. Dix. Adam répète : dix. Il a compté des objets. Les galets sont lisses. Tu as dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1285,6 +1301,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam est au bord de la mer avec maman. Des galets sont sur le sable.
+maman|On compte des objets.
+narrateur|Adam touche un galet. Un. Il touche un autre. Deux. Trois. Quatre. Cinq.
+enfant-m|Cinq galets. Maman en pose encore. Six. Sept. Huit. Neuf. Dix.
+narrateur|Adam répète : dix. Il a compté des objets. Les galets sont lisses.
+maman|Tu as dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1461,6 +1487,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Adam touche les galets. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1625,6 +1656,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a compté des objets. Il a dit le nombre. Cinq, puis dix.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1823,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range trois galets dans le seau. Adam donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1990,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2030,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1311,6 +1316,7 @@
 maman|Tu as dit le nombre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1494,6 +1500,7 @@
           <t>narrateur|Adam touche les galets. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1661,6 +1668,7 @@
           <t>narrateur|Adam a compté des objets. Il a dit le nombre. Cinq, puis dix.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1828,6 +1836,7 @@
           <t>narrateur|Maman range trois galets dans le seau. Adam donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1995,6 +2004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2013,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2037,6 +2047,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2238,6 +2262,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adam compte les galets</t>
+          <t>Aniss compte les galets</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le vent apporte le sel. Aniss touche les galets lisses. Il compte cinq, puis dix. Papa et maman disent le nombre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam est au bord de la mer avec maman. Des galets sont sur le sable. On compte des objets. Adam touche un galet. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Maman en pose encore. Six. Sept. Huit. Neuf. Dix. Adam répète : dix. Il a compté des objets. Les galets sont lisses. Tu as dit le nombre.</t>
+          <t>Le vent apporte une odeur de sel. Le sable est froid sous les pieds. Il colle un peu aux orteils. Une vague finit tout loin. Elle fait un petit chuintement. Un seau bleu repose près d'une serviette. La serviette est rayée, un peu rêche. Un coquillage blanc attend dans le seau. Il est léger et mat. Aniss, tu sens le sel ? Oui, maman. Ça pique un peu. Le seau est là. Les galets brillent. En ce moment, Aniss s'agenouille. Des galets sont sur le sable. Ils sont lisses et gris. On compte des objets. On touche. On dit le nombre. Aniss touche un galet. Un. Il en touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Tu as dit le nombre. Maman en pose encore près du seau. Les galets tapent tout doux. Six. Sept. Huit. Neuf. Dix. Dix. Tu as compté des objets. Dix galets. Bravo, Aniss. Tu as fait du bon travail. Aniss pose les galets dans le seau. Un. Deux. Trois. Quatre. Cinq. Le seau devient un peu lourd. Les objets sont là. On peut dire le nombre. Une vague chuchote encore. Le coquillage reste blanc. Le galet est lisse, hein ? Oui. Lisse. On rentre le seau ? Oui, papa. Maman pose des coquillages près du seau. Ils sont blancs et légers. On compte aussi les coquillages. Aniss touche un coquillage. Un. Deux. Trois. Quatre. Cinq. Cinq coquillages. Tu dis le nombre. Cinq. Tu as compté des objets. Le sable reste froid. La vague chuchote encore. Galets et coquillages. J'ai dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1308,15 +1320,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Adam est au bord de la mer avec maman. Des galets sont sur le sable.
-maman|On compte des objets.
-narrateur|Adam touche un galet. Un. Il touche un autre. Deux. Trois. Quatre. Cinq.
-enfant-m|Cinq galets. Maman en pose encore. Six. Sept. Huit. Neuf. Dix.
-narrateur|Adam répète : dix. Il a compté des objets. Les galets sont lisses.
-maman|Tu as dit le nombre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le vent apporte une odeur de sel.
+narrateur|Le sable est froid sous les pieds.
+narrateur|Il colle un peu aux orteils.
+narrateur|Une vague finit tout loin.
+narrateur|Elle fait un petit chuintement.
+narrateur|Un seau bleu repose près d'une serviette.
+narrateur|La serviette est rayée, un peu rêche.
+narrateur|Un coquillage blanc attend dans le seau.
+narrateur|Il est léger et mat.
+maman|Aniss, tu sens le sel ?
+enfant-m|Oui, maman.
+enfant-m|Ça pique un peu.
+papa|Le seau est là.
+maman|Les galets brillent.
+narrateur|En ce moment, Aniss s'agenouille.
+narrateur|Des galets sont sur le sable.
+narrateur|Ils sont lisses et gris.
+papa|On compte des objets.
+maman|On touche. On dit le nombre.
+narrateur|Aniss touche un galet.
+enfant-m|Un.
+narrateur|Il en touche un autre.
+enfant-m|Deux.
+enfant-m|Trois.
+enfant-m|Quatre.
+enfant-m|Cinq.
+papa|Cinq galets.
+maman|Tu as dit le nombre.
+narrateur|Maman en pose encore près du seau.
+narrateur|Les galets tapent tout doux.
+enfant-m|Six.
+enfant-m|Sept.
+enfant-m|Huit.
+enfant-m|Neuf.
+enfant-m|Dix.
+papa|Dix.
+maman|Tu as compté des objets.
+enfant-m|Dix galets.
+papa|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Aniss pose les galets dans le seau.
+narrateur|Un. Deux. Trois. Quatre. Cinq.
+narrateur|Le seau devient un peu lourd.
+maman|Les objets sont là.
+papa|On peut dire le nombre.
+narrateur|Une vague chuchote encore.
+narrateur|Le coquillage reste blanc.
+maman|Le galet est lisse, hein ?
+enfant-m|Oui. Lisse.
+papa|On rentre le seau ?
+enfant-m|Oui, papa.
+narrateur|Maman pose des coquillages près du seau.
+narrateur|Ils sont blancs et légers.
+maman|On compte aussi les coquillages.
+narrateur|Aniss touche un coquillage.
+enfant-m|Un. Deux. Trois. Quatre. Cinq.
+papa|Cinq coquillages.
+maman|Tu dis le nombre.
+enfant-m|Cinq.
+papa|Tu as compté des objets.
+narrateur|Le sable reste froid.
+narrateur|La vague chuchote encore.
+maman|Galets et coquillages.
+enfant-m|J'ai dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1341,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Adam touche les galets. Que fait-il ?</t>
+          <t>Aniss touche les galets. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1497,10 +1566,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Adam touche les galets. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss touche les galets.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1525,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam a compté des objets. Il a dit le nombre. Cinq, puis dix.</t>
+          <t>Aniss a compté des objets. Il a dit le nombre. Cinq, puis dix. Tu as compté les galets ? Oui, maman. Bravo, Aniss. Tu as fait du bon travail. Le seau bleu repose près de la serviette. Les galets sont lisses. Le seau est lourd ? Un peu. Un galet gris brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1665,10 +1734,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam a compté des objets. Il a dit le nombre. Cinq, puis dix.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a compté des objets.
+narrateur|Il a dit le nombre.
+narrateur|Cinq, puis dix.
+maman|Tu as compté les galets ?
+enfant-m|Oui, maman.
+papa|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Le seau bleu repose près de la serviette.
+narrateur|Les galets sont lisses.
+maman|Le seau est lourd ?
+enfant-m|Un peu.
+narrateur|Un galet gris brille encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1693,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range trois galets dans le seau. Adam donne la main.</t>
+          <t>Aniss essuie ses mains au sable. Je te tiens le seau ? Oui, maman. Maman tient l'anse. L'anse est un peu froide. Tu as fini de compter ? Oui, papa. Bravo. Le vent sent encore le sel. On garde un galet ? Oui. Le galet tient dans la paume.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,10 +1912,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range trois galets dans le seau. Adam donne la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss essuie ses mains au sable.
+maman|Je te tiens le seau ?
+enfant-m|Oui, maman.
+narrateur|Maman tient l'anse.
+narrateur|L'anse est un peu froide.
+papa|Tu as fini de compter ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Le vent sent encore le sel.
+maman|On garde un galet ?
+enfant-m|Oui.
+narrateur|Le galet tient dans la paume.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1861,7 +1950,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss tient un galet lisse. Le seau cloche un peu. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2001,10 +2090,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Aniss tient un galet lisse.
+narrateur|Le seau cloche un peu.
+maman|Merci d'avoir compté.
+papa|On touche. On dit le nombre.
+enfant-m|Oui.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2061,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aniss compte les galets</t>
+          <t>Les galets lisses de Nino</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Le vent apporte le sel. Aniss touche les galets lisses. Il compte cinq, puis dix. Papa et maman disent le nombre.</t>
+          <t>L'écume laisse un collier blanc. Nino touche les galets. Cinq, puis dix. Il dit le nombre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le vent apporte une odeur de sel. Le sable est froid sous les pieds. Il colle un peu aux orteils. Une vague finit tout loin. Elle fait un petit chuintement. Un seau bleu repose près d'une serviette. La serviette est rayée, un peu rêche. Un coquillage blanc attend dans le seau. Il est léger et mat. Aniss, tu sens le sel ? Oui, maman. Ça pique un peu. Le seau est là. Les galets brillent. En ce moment, Aniss s'agenouille. Des galets sont sur le sable. Ils sont lisses et gris. On compte des objets. On touche. On dit le nombre. Aniss touche un galet. Un. Il en touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Tu as dit le nombre. Maman en pose encore près du seau. Les galets tapent tout doux. Six. Sept. Huit. Neuf. Dix. Dix. Tu as compté des objets. Dix galets. Bravo, Aniss. Tu as fait du bon travail. Aniss pose les galets dans le seau. Un. Deux. Trois. Quatre. Cinq. Le seau devient un peu lourd. Les objets sont là. On peut dire le nombre. Une vague chuchote encore. Le coquillage reste blanc. Le galet est lisse, hein ? Oui. Lisse. On rentre le seau ? Oui, papa. Maman pose des coquillages près du seau. Ils sont blancs et légers. On compte aussi les coquillages. Aniss touche un coquillage. Un. Deux. Trois. Quatre. Cinq. Cinq coquillages. Tu dis le nombre. Cinq. Tu as compté des objets. Le sable reste froid. La vague chuchote encore. Galets et coquillages. J'ai dit le nombre.</t>
+          <t>L'écume laisse un collier blanc sur le sable. Le sel pique un peu les lèvres. Le sable mouillé est froid sous les pieds. Un goéland crie, tout loin. Un seau bleu penche près d'une dune. Une coquille rose brille. Le vent sent la mer. Tu as vu le collier d'écume, Nino ? Oui, maman. Il est blanc. La mer le pose, puis le reprend. En ce moment, Nino s'assoit sur le sable. Des galets sont là, tout près. Ils sont gris et lisses. On va compter des objets. Des galets. Des galets. Nino touche un galet. Il est froid et lisse. Un. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Nino. Tu as compté des objets. C'est du bon travail. Les galets sont lisses. Ils sentent le sel. On les pose en ligne ? Oui, maman. Nino pose les galets. Un, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix galets. Oui. Cinq, puis dix. Une vague arrive tout près. Elle mouille le bord du seau. Le seau est un peu mouillé. Les galets aussi. Nino prend la coquille rose. Elle est légère. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le vent sent encore la mer. Le collier d'écume a bougé. Tu mets la coquille près du seau ? Oui, maman. Nino pose la coquille. Elle fait un petit bruit. Tu as compté des objets. Dix galets. Oui. Tu as dit le nombre. Une vague revient, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam est au bord de la mer avec maman. Des galets sont sur le sable. Maman dit : on compte des objets. Adam touche un galet. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Adam dit : cinq galets. Maman en pose encore. Six. Sept. Huit. Neuf. Dix. Adam répète : dix. Il a compté des objets. Les galets sont lisses. Maman dit : tu as dit le nombre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'écume laisse un collier blanc sur le sable. Le sel pique un peu les lèvres. Le sable mouillé est froid sous les pieds. Un goéland crie, tout loin. Un seau bleu penche près d'une dune. Une coquille rose brille. Le vent sent la mer. Tu as vu le collier d'écume, Nino ? Oui, maman. Il est blanc. La mer le pose, puis le reprend. En ce moment, Nino s'assoit sur le sable. Des galets sont là, tout près. Ils sont gris et lisses. On va compter des objets. Des galets. Des galets. Nino touche un galet. Il est froid et lisse. Un. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Nino. Tu as compté des objets. C'est du bon travail. Les galets sont lisses. Ils sentent le sel. On les pose en ligne ? Oui, maman. Nino pose les galets. Un, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix galets. Oui. Cinq, puis dix. Une vague arrive tout près. Elle mouille le bord du seau. Le seau est un peu mouillé. Les galets aussi. Nino prend la coquille rose. Elle est légère. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le vent sent encore la mer. Le collier d'écume a bougé. Tu mets la coquille près du seau ? Oui, maman. Nino pose la coquille. Elle fait un petit bruit. Tu as compté des objets. Dix galets. Oui. Tu as dit le nombre. Une vague revient, tout doux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1320,70 +1320,82 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le vent apporte une odeur de sel.
-narrateur|Le sable est froid sous les pieds.
-narrateur|Il colle un peu aux orteils.
-narrateur|Une vague finit tout loin.
-narrateur|Elle fait un petit chuintement.
-narrateur|Un seau bleu repose près d'une serviette.
-narrateur|La serviette est rayée, un peu rêche.
-narrateur|Un coquillage blanc attend dans le seau.
-narrateur|Il est léger et mat.
-maman|Aniss, tu sens le sel ?
+          <t>narrateur|L'écume laisse un collier blanc sur le sable.
+narrateur|Le sel pique un peu les lèvres.
+narrateur|Le sable mouillé est froid sous les pieds.
+narrateur|Un goéland crie, tout loin.
+narrateur|Un seau bleu penche près d'une dune.
+narrateur|Une coquille rose brille.
+narrateur|Le vent sent la mer.
+maman|Tu as vu le collier d'écume, Nino ?
 enfant-m|Oui, maman.
-enfant-m|Ça pique un peu.
-papa|Le seau est là.
-maman|Les galets brillent.
-narrateur|En ce moment, Aniss s'agenouille.
-narrateur|Des galets sont sur le sable.
-narrateur|Ils sont lisses et gris.
-papa|On compte des objets.
-maman|On touche. On dit le nombre.
-narrateur|Aniss touche un galet.
+enfant-m|Il est blanc.
+maman|La mer le pose, puis le reprend.
+narrateur|En ce moment, Nino s'assoit sur le sable.
+narrateur|Des galets sont là, tout près.
+narrateur|Ils sont gris et lisses.
+maman|On va compter des objets.
+maman|Des galets.
+enfant-m|Des galets.
+narrateur|Nino touche un galet.
+narrateur|Il est froid et lisse.
+maman|Un.
 enfant-m|Un.
-narrateur|Il en touche un autre.
+narrateur|Il touche un autre.
 enfant-m|Deux.
 enfant-m|Trois.
 enfant-m|Quatre.
 enfant-m|Cinq.
-papa|Cinq galets.
+enfant-m|Cinq galets.
 maman|Tu as dit le nombre.
-narrateur|Maman en pose encore près du seau.
-narrateur|Les galets tapent tout doux.
+maman|Cinq.
+narrateur|Maman en pose encore.
+maman|On continue.
 enfant-m|Six.
 enfant-m|Sept.
 enfant-m|Huit.
 enfant-m|Neuf.
 enfant-m|Dix.
-papa|Dix.
+enfant-m|Dix.
+maman|Tu as dit le nombre.
+maman|Dix.
+maman|Bravo, Nino.
+maman|Tu as compté des objets.
+maman|C'est du bon travail.
+narrateur|Les galets sont lisses.
+narrateur|Ils sentent le sel.
+maman|On les pose en ligne ?
+enfant-m|Oui, maman.
+narrateur|Nino pose les galets.
+enfant-m|Un, deux, trois, quatre, cinq.
+enfant-m|Six, sept, huit, neuf, dix.
+maman|Les objets sont là.
+maman|Tu les as comptés.
+enfant-m|Dix galets.
+maman|Oui.
+maman|Cinq, puis dix.
+narrateur|Une vague arrive tout près.
+narrateur|Elle mouille le bord du seau.
+maman|Le seau est un peu mouillé.
+enfant-m|Les galets aussi.
+narrateur|Nino prend la coquille rose.
+narrateur|Elle est légère.
+maman|Tu as fini de compter ?
+enfant-m|Oui, maman.
+enfant-m|Dix.
+maman|Bravo.
+maman|Tu as compté des objets.
+narrateur|Le vent sent encore la mer.
+narrateur|Le collier d'écume a bougé.
+maman|Tu mets la coquille près du seau ?
+enfant-m|Oui, maman.
+narrateur|Nino pose la coquille.
+narrateur|Elle fait un petit bruit.
 maman|Tu as compté des objets.
 enfant-m|Dix galets.
-papa|Bravo, Aniss.
-papa|Tu as fait du bon travail.
-narrateur|Aniss pose les galets dans le seau.
-narrateur|Un. Deux. Trois. Quatre. Cinq.
-narrateur|Le seau devient un peu lourd.
-maman|Les objets sont là.
-papa|On peut dire le nombre.
-narrateur|Une vague chuchote encore.
-narrateur|Le coquillage reste blanc.
-maman|Le galet est lisse, hein ?
-enfant-m|Oui. Lisse.
-papa|On rentre le seau ?
-enfant-m|Oui, papa.
-narrateur|Maman pose des coquillages près du seau.
-narrateur|Ils sont blancs et légers.
-maman|On compte aussi les coquillages.
-narrateur|Aniss touche un coquillage.
-enfant-m|Un. Deux. Trois. Quatre. Cinq.
-papa|Cinq coquillages.
-maman|Tu dis le nombre.
-enfant-m|Cinq.
-papa|Tu as compté des objets.
-narrateur|Le sable reste froid.
-narrateur|La vague chuchote encore.
-maman|Galets et coquillages.
-enfant-m|J'ai dit le nombre.</t>
+maman|Oui.
+maman|Tu as dit le nombre.
+narrateur|Une vague revient, tout doux.</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1422,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aniss touche les galets. Que fait-il ?</t>
+          <t>Nino touche les galets. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Adam touche les galets. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino touche les galets. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1566,7 +1578,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Aniss touche les galets.
+          <t>narrateur|Nino touche les galets.
 narrateur|Que fait-il ?</t>
         </is>
       </c>
@@ -1594,12 +1606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a compté des objets. Il a dit le nombre. Cinq, puis dix. Tu as compté les galets ? Oui, maman. Bravo, Aniss. Tu as fait du bon travail. Le seau bleu repose près de la serviette. Les galets sont lisses. Le seau est lourd ? Un peu. Un galet gris brille encore.</t>
+          <t>Nino a compté des objets. Il a dit le nombre. Cinq, puis dix. Dix galets. Bravo, Nino. Dix. Tu as fait du bon travail. La ligne de galets brille. Le goéland crie encore, tout loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam a compté des objets. Il a dit le nombre. Cinq, puis dix.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a compté des objets. Il a dit le nombre. Cinq, puis dix. Dix galets. Bravo, Nino. Dix. Tu as fait du bon travail. La ligne de galets brille. Le goéland crie encore, tout loin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1734,18 +1746,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aniss a compté des objets.
+          <t>narrateur|Nino a compté des objets.
 narrateur|Il a dit le nombre.
 narrateur|Cinq, puis dix.
-maman|Tu as compté les galets ?
-enfant-m|Oui, maman.
-papa|Bravo, Aniss.
-papa|Tu as fait du bon travail.
-narrateur|Le seau bleu repose près de la serviette.
-narrateur|Les galets sont lisses.
-maman|Le seau est lourd ?
-enfant-m|Un peu.
-narrateur|Un galet gris brille encore.</t>
+maman|Dix galets.
+maman|Bravo, Nino.
+enfant-m|Dix.
+maman|Tu as fait du bon travail.
+narrateur|La ligne de galets brille.
+narrateur|Le goéland crie encore, tout loin.</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1781,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aniss essuie ses mains au sable. Je te tiens le seau ? Oui, maman. Maman tient l'anse. L'anse est un peu froide. Tu as fini de compter ? Oui, papa. Bravo. Le vent sent encore le sel. On garde un galet ? Oui. Le galet tient dans la paume.</t>
+          <t>On range trois galets dans le seau ? Oui, maman. Maman range trois galets. Nino donne la main. Tu as fini de compter ? Oui. Dix. Bravo. Le seau bleu penche un peu. Le sable reste froid sous les pieds. On rentre les pieds sableux ? Oui, maman. Ils marchent près de l'eau. Le seau tape contre la jambe. Tu as bien compté. Cinq, puis dix.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range trois galets dans le seau. Adam donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range trois galets dans le seau ? Oui, maman. Maman range trois galets. Nino donne la main. Tu as fini de compter ? Oui. Dix. Bravo. Le seau bleu penche un peu. Le sable reste froid sous les pieds. On rentre les pieds sableux ? Oui, maman. Ils marchent près de l'eau. Le seau tape contre la jambe. Tu as bien compté. Cinq, puis dix.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1912,18 +1921,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aniss essuie ses mains au sable.
-maman|Je te tiens le seau ?
+          <t>maman|On range trois galets dans le seau ?
 enfant-m|Oui, maman.
-narrateur|Maman tient l'anse.
-narrateur|L'anse est un peu froide.
-papa|Tu as fini de compter ?
-enfant-m|Oui, papa.
-papa|Bravo.
-narrateur|Le vent sent encore le sel.
-maman|On garde un galet ?
+narrateur|Maman range trois galets.
+narrateur|Nino donne la main.
+maman|Tu as fini de compter ?
 enfant-m|Oui.
-narrateur|Le galet tient dans la paume.</t>
+enfant-m|Dix.
+maman|Bravo.
+narrateur|Le seau bleu penche un peu.
+narrateur|Le sable reste froid sous les pieds.
+maman|On rentre les pieds sableux ?
+enfant-m|Oui, maman.
+narrateur|Ils marchent près de l'eau.
+narrateur|Le seau tape contre la jambe.
+maman|Tu as bien compté.
+enfant-m|Cinq, puis dix.</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Aniss tient un galet lisse. Le seau cloche un peu. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
+          <t>L'écume a bougé. Dix galets. Tu as compté des objets. Bravo, Nino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'écume a bougé. Dix galets. Tu as compté des objets. Bravo, Nino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,11 +2103,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Aniss tient un galet lisse.
-narrateur|Le seau cloche un peu.
-maman|Merci d'avoir compté.
-papa|On touche. On dit le nombre.
-enfant-m|Oui.
+          <t>narrateur|L'écume a bougé.
+enfant-m|Dix galets.
+maman|Tu as compté des objets.
+maman|Bravo, Nino.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2116,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2173,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'écume laisse un collier blanc sur le sable. Le sel pique un peu les lèvres. Le sable mouillé est froid sous les pieds. Un goéland crie, tout loin. Un seau bleu penche près d'une dune. Une coquille rose brille. Le vent sent la mer. Tu as vu le collier d'écume, Nino ? Oui, maman. Il est blanc. La mer le pose, puis le reprend. En ce moment, Nino s'assoit sur le sable. Des galets sont là, tout près. Ils sont gris et lisses. On va compter des objets. Des galets. Des galets. Nino touche un galet. Il est froid et lisse. Un. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Nino. Tu as compté des objets. C'est du bon travail. Les galets sont lisses. Ils sentent le sel. On les pose en ligne ? Oui, maman. Nino pose les galets. Un, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix galets. Oui. Cinq, puis dix. Une vague arrive tout près. Elle mouille le bord du seau. Le seau est un peu mouillé. Les galets aussi. Nino prend la coquille rose. Elle est légère. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le vent sent encore la mer. Le collier d'écume a bougé. Tu mets la coquille près du seau ? Oui, maman. Nino pose la coquille. Elle fait un petit bruit. Tu as compté des objets. Dix galets. Oui. Tu as dit le nombre. Une vague revient, tout doux.</t>
+          <t>L'écume laisse un collier blanc sur le sable. Le sel pique un peu les lèvres. Le sable mouillé est froid sous les pieds. Un goéland crie, tout loin. Un seau bleu penche près d'une dune. Une coquille rose brille. Le vent sent la mer. Tu as vu le collier d'écume, Nino ? Oui, maman. Il est blanc. La mer le pose, puis le reprend. En ce moment, Nino s'assoit sur le sable. Des galets sont là, tout près. Ils sont gris et lisses. On va compter des objets. Des galets. Des galets. Nino touche un galet. Il est froid et lisse. Un. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Nino. Tu as compté des objets. Les galets sont lisses. Ils sentent le sel. On les pose en ligne ? Oui, maman. Nino pose les galets. Un, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix galets. Oui. Cinq, puis dix. Une vague arrive tout près. Elle mouille le bord du seau. Le seau est un peu mouillé. Les galets aussi. Nino prend la coquille rose. Elle est légère. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le vent sent encore la mer. Le collier d'écume a bougé. Tu mets la coquille près du seau ? Oui, maman. Nino pose la coquille. Elle fait un petit bruit. Tu as compté des objets. Dix galets. Oui. Tu as dit le nombre. Une vague revient, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>L'écume laisse un collier blanc sur le sable. Le sel pique un peu les lèvres. Le sable mouillé est froid sous les pieds. Un goéland crie, tout loin. Un seau bleu penche près d'une dune. Une coquille rose brille. Le vent sent la mer. Tu as vu le collier d'écume, Nino ? Oui, maman. Il est blanc. La mer le pose, puis le reprend. En ce moment, Nino s'assoit sur le sable. Des galets sont là, tout près. Ils sont gris et lisses. On va compter des objets. Des galets. Des galets. Nino touche un galet. Il est froid et lisse. Un. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Nino. Tu as compté des objets. C'est du bon travail. Les galets sont lisses. Ils sentent le sel. On les pose en ligne ? Oui, maman. Nino pose les galets. Un, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix galets. Oui. Cinq, puis dix. Une vague arrive tout près. Elle mouille le bord du seau. Le seau est un peu mouillé. Les galets aussi. Nino prend la coquille rose. Elle est légère. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le vent sent encore la mer. Le collier d'écume a bougé. Tu mets la coquille près du seau ? Oui, maman. Nino pose la coquille. Elle fait un petit bruit. Tu as compté des objets. Dix galets. Oui. Tu as dit le nombre. Une vague revient, tout doux.</t>
+          <t>L'écume laisse un collier blanc sur le sable. Le sel pique un peu les lèvres. Le sable mouillé est froid sous les pieds. Un goéland crie, tout loin. Un seau bleu penche près d'une dune. Une coquille rose brille. Le vent sent la mer. Tu as vu le collier d'écume, Nino ? Oui, maman. Il est blanc. La mer le pose, puis le reprend. En ce moment, Nino s'assoit sur le sable. Des galets sont là, tout près. Ils sont gris et lisses. On va compter des objets. Des galets. Des galets. Nino touche un galet. Il est froid et lisse. Un. Un. Il touche un autre. Deux. Trois. Quatre. Cinq. Cinq galets. Tu as dit le nombre. Cinq. Maman en pose encore. On continue. Six. Sept. Huit. Neuf. Dix. Dix. Tu as dit le nombre. Dix. Bravo, Nino. Tu as compté des objets. Les galets sont lisses. Ils sentent le sel. On les pose en ligne ? Oui, maman. Nino pose les galets. Un, deux, trois, quatre, cinq. Six, sept, huit, neuf, dix. Les objets sont là. Tu les as comptés. Dix galets. Oui. Cinq, puis dix. Une vague arrive tout près. Elle mouille le bord du seau. Le seau est un peu mouillé. Les galets aussi. Nino prend la coquille rose. Elle est légère. Tu as fini de compter ? Oui, maman. Dix. Bravo. Tu as compté des objets. Le vent sent encore la mer. Le collier d'écume a bougé. Tu mets la coquille près du seau ? Oui, maman. Nino pose la coquille. Elle fait un petit bruit. Tu as compté des objets. Dix galets. Oui. Tu as dit le nombre. Une vague revient, tout doux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,7 +1361,6 @@
 maman|Dix.
 maman|Bravo, Nino.
 maman|Tu as compté des objets.
-maman|C'est du bon travail.
 narrateur|Les galets sont lisses.
 narrateur|Ils sentent le sel.
 maman|On les pose en ligne ?
@@ -1606,12 +1605,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a compté des objets. Il a dit le nombre. Cinq, puis dix. Dix galets. Bravo, Nino. Dix. Tu as fait du bon travail. La ligne de galets brille. Le goéland crie encore, tout loin.</t>
+          <t>Nino a compté des objets. Il a dit le nombre. Cinq, puis dix. Dix galets. Bravo, Nino. Dix. La ligne de galets brille. Le goéland crie encore, tout loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino a compté des objets. Il a dit le nombre. Cinq, puis dix. Dix galets. Bravo, Nino. Dix. Tu as fait du bon travail. La ligne de galets brille. Le goéland crie encore, tout loin.</t>
+          <t>Nino a compté des objets. Il a dit le nombre. Cinq, puis dix. Dix galets. Bravo, Nino. Dix. La ligne de galets brille. Le goéland crie encore, tout loin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,7 +1751,6 @@
 maman|Dix galets.
 maman|Bravo, Nino.
 enfant-m|Dix.
-maman|Tu as fait du bon travail.
 narrateur|La ligne de galets brille.
 narrateur|Le goéland crie encore, tout loin.</t>
         </is>
@@ -1963,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'écume a bougé. Dix galets. Tu as compté des objets. Bravo, Nino. L'histoire est finie.</t>
+          <t>L'écume a bougé. Dix galets. Tu as compté des objets. Bravo, Nino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>L'écume a bougé. Dix galets. Tu as compté des objets. Bravo, Nino. L'histoire est finie.</t>
+          <t>L'écume a bougé. Dix galets. Tu as compté des objets. Bravo, Nino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,8 +2104,7 @@
           <t>narrateur|L'écume a bougé.
 enfant-m|Dix galets.
 maman|Tu as compté des objets.
-maman|Bravo, Nino.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Nino.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2175,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>plage</t>
+          <t>plage, fin de matinée</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adam, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
